--- a/outputs/model_results/MCLR/benchmark_validation_results.xlsx
+++ b/outputs/model_results/MCLR/benchmark_validation_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,121 +460,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4863636363636363</v>
+        <v>0.4874331550802139</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01540046604581199</v>
+        <v>0.01692642196311916</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4533229767270047</v>
+        <v>0.4541770724189236</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01845294370107991</v>
+        <v>0.02134750992836667</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5973262032085562</v>
+        <v>0.5965240641711229</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02554840467506149</v>
+        <v>0.02664422068096921</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Model 1 bis</t>
+          <t>Model 2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4850267379679144</v>
+        <v>0.417379679144385</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01715715211460489</v>
+        <v>0.01062813203976032</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4526213725817539</v>
+        <v>0.3510258085966012</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01983880224108373</v>
+        <v>0.0102902705639292</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5981283422459893</v>
+        <v>0.7037433155080215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02753815994363639</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Model 1 ter</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.4858288770053477</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.01782642599014255</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4521315945220209</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.01971642270406235</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.5983957219251337</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.02829048850961522</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Model 2</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.417379679144385</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.01062813203976032</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3510258085966012</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0102902705639292</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.7037433155080215</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.01795131490680387</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Model 2 bis</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.417379679144385</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.01062813203976032</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.3510258085966012</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.0102902705639292</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.7037433155080215</v>
-      </c>
-      <c r="G6" t="n">
         <v>0.01795131490680387</v>
       </c>
     </row>
